--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260623.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.62%</t>
+          <t>26.55%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>18,275</t>
+          <t>115,830</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>8.37%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>115,830</t>
+          <t>18,275</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.63%</t>
+          <t>8.28%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.74%</t>
+          <t>7.22%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>5.32%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>52,335</t>
+          <t>68,880</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>68,880</t>
+          <t>52,335</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>171,234,091</t>
+          <t>166,669,167</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -924,73 +924,73 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>59,155</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>59,155</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1034,46 +1034,46 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,196</t>
+          <t>41,980</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>41,980</t>
+          <t>68,868</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,66 +1085,66 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>68,868</t>
+          <t>11,196</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,738</t>
+          <t>2,942,745</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>22,867</t>
+          <t>24,738</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,521</t>
+          <t>22,867</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,665</t>
+          <t>18,521</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1254,51 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>50,090</t>
+          <t>13,665</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>969,568</t>
+          <t>50,090</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1319,28 +1319,6 @@
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>1,949,102</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
